--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,12 +702,16 @@
           <t>NSE:BHEL26SEP420CE</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:16:56</t>
+        </is>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -730,8 +734,123 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:16:56</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>585</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="H3" t="n">
+        <v>580</v>
+      </c>
+      <c r="I3" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1225</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="S3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NSE:HINDZINC26SEP580CE</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AK4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -851,6 +851,125 @@
           <t>2026-09-29</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:18:32</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1172.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1180</v>
+      </c>
+      <c r="I4" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="K4" t="n">
+        <v>47.69</v>
+      </c>
+      <c r="L4" t="n">
+        <v>53.38</v>
+      </c>
+      <c r="M4" t="n">
+        <v>60.98</v>
+      </c>
+      <c r="N4" t="n">
+        <v>625</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="S4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="U4" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:LODHA26SEP1180CE</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -829,6 +829,16 @@
           <t>NSE:HINDZINC26SEP580CE</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:20:05</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -850,6 +860,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -940,12 +956,16 @@
           <t>NSE:LODHA26SEP1180CE</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:20:05</t>
+        </is>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -968,8 +988,12 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>38.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK4"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -994,6 +994,125 @@
       <c r="AK4" t="n">
         <v>38.2</v>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:35:37</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>781.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="H5" t="n">
+        <v>780</v>
+      </c>
+      <c r="I5" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="K5" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="L5" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="M5" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1225</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="S5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="U5" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:SONACOMS26SEP780CE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,12 +1083,6 @@
           <t>NSE:SONACOMS26SEP780CE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1111,8 +1105,125 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:46:22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1248.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1240</v>
+      </c>
+      <c r="I6" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="K6" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="L6" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="M6" t="n">
+        <v>60.64</v>
+      </c>
+      <c r="N6" t="n">
+        <v>550</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="S6" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>53.26</v>
+      </c>
+      <c r="U6" t="n">
+        <v>27</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:UNOMINDA26SEP1240CE</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,6 +1083,16 @@
           <t>NSE:SONACOMS26SEP780CE</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:47:55</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1104,6 +1114,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -1194,12 +1210,6 @@
           <t>NSE:UNOMINDA26SEP1240CE</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1222,8 +1232,228 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:47:55</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>46880</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="H7" t="n">
+        <v>47000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1311.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>974.86</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1611.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1791.68</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2031.92</v>
+      </c>
+      <c r="N7" t="n">
+        <v>25</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="S7" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="U7" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:BOSCHLTD26SEP47000CE</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:47:55</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>331.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>330</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="K8" t="n">
+        <v>13</v>
+      </c>
+      <c r="L8" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="M8" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3125</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="S8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="U8" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>E-Commerce</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:NYKAA26SEP330CE</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK8"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1454,6 +1454,125 @@
           <t>2026-09-29</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:49:30</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1320</v>
+      </c>
+      <c r="I9" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="K9" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="L9" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="M9" t="n">
+        <v>61.51</v>
+      </c>
+      <c r="N9" t="n">
+        <v>550</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="S9" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>44.83</v>
+      </c>
+      <c r="U9" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>E-Commerce</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:NAUKRI26SEP1320CE</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1543,12 +1543,16 @@
           <t>NSE:NAUKRI26SEP1320CE</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:51:03</t>
+        </is>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1571,8 +1575,12 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
+      <c r="AJ9" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>41.05</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1210,6 +1210,16 @@
           <t>NSE:UNOMINDA26SEP1240CE</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:52:38</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1231,6 +1241,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>40.5</v>
       </c>
     </row>
     <row r="7">
@@ -1321,6 +1337,16 @@
           <t>NSE:BOSCHLTD26SEP47000CE</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:52:38</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1342,6 +1368,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1349.45</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1270</v>
       </c>
     </row>
     <row r="8">
@@ -1432,6 +1464,16 @@
           <t>NSE:NYKAA26SEP330CE</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:52:38</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1453,6 +1495,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="9">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1215,11 +1215,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-09-02 09:52:38</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1467,11 +1463,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>Expired (no SL/Target hit)</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-09-02 09:52:38</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1215,7 +1215,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1587,11 +1586,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-09-02 09:51:03</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1337,11 +1337,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-02 09:52:38</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1586,7 +1582,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -702,9 +702,14 @@
           <t>NSE:BHEL26SEP420CE</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:04:38</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 1 Hit</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1337,7 +1342,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1464,6 +1464,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:05:09</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1591,6 +1591,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:06:42</t>
+        </is>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1614,10 +1619,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>41.3</v>
+        <v>44.75</v>
       </c>
       <c r="AK9" t="n">
-        <v>41.05</v>
+        <v>39.2</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1591,11 +1591,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-09-02 10:06:42</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1591,7 +1591,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:09:46</t>
+        </is>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1464,11 +1464,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-09-02 10:05:09</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1464,7 +1464,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:19:18</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1488,7 +1492,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>10.85</v>
+        <v>11.4</v>
       </c>
       <c r="AK8" t="n">
         <v>9.699999999999999</v>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1220,6 +1220,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:20:50</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1220,11 +1220,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-09-02 10:20:50</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1220,7 +1220,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:27:03</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1244,7 +1248,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>43.05</v>
+        <v>43.3</v>
       </c>
       <c r="AK6" t="n">
         <v>40.5</v>
@@ -1590,11 +1594,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>Expired (no SL/Target hit)</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-09-02 10:09:46</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1596,6 +1596,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:30:17</t>
+        </is>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1619,7 +1624,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>44.75</v>
+        <v>46.55</v>
       </c>
       <c r="AK9" t="n">
         <v>39.2</v>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1220,11 +1220,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-09-02 10:27:03</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1215,12 +1215,16 @@
           <t>NSE:UNOMINDA26SEP1240CE</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-09-02 11:04:25</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1247,7 +1251,7 @@
         <v>43.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>40.5</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="7">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1347,6 +1347,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-02 11:24:38</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1349.45</v>
+        <v>1311.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1270</v>
+        <v>1311.2</v>
       </c>
     </row>
     <row r="8">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1347,11 +1347,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-02 11:24:38</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1225,6 +1225,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-09-02 11:29:18</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1347,7 +1352,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1352,6 +1352,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-02 11:44:18</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1378,7 +1383,7 @@
         <v>1311.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1311.2</v>
+        <v>1132.35</v>
       </c>
     </row>
     <row r="8">
@@ -1596,9 +1601,14 @@
           <t>NSE:NAUKRI26SEP1320CE</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-02 11:44:08</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 1 Hit</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1352,11 +1352,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-02 11:44:18</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,7 +1352,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1640,6 +1639,125 @@
       <c r="AK9" t="n">
         <v>39.2</v>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:23:22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>782</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>780</v>
+      </c>
+      <c r="I10" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="K10" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="L10" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="M10" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1225</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="S10" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>43.11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:SONACOMS26SEP780CE</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1728,12 +1728,16 @@
           <t>NSE:SONACOMS26SEP780CE</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:40:32</t>
+        </is>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1756,8 +1760,12 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
+      <c r="AJ10" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>25.55</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1733,11 +1733,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-09-02 12:40:32</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1352,6 +1352,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:45:15</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1733,7 +1738,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:45:15</t>
+        </is>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1352,11 +1352,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-02 12:45:15</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1736,11 +1732,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>Expired (no SL/Target hit)</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-09-02 12:45:15</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -961,9 +961,14 @@
           <t>NSE:LODHA26SEP1180CE</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:50:23</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 1 Hit</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1352,7 +1357,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK10"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1766,6 +1766,125 @@
       <c r="AK10" t="n">
         <v>25.55</v>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:16:23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1246</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1240</v>
+      </c>
+      <c r="I11" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="K11" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="L11" t="n">
+        <v>53.87</v>
+      </c>
+      <c r="M11" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>550</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>52.37</v>
+      </c>
+      <c r="U11" t="n">
+        <v>26</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:UNOMINDA26SEP1240CE</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1855,12 +1855,16 @@
           <t>NSE:UNOMINDA26SEP1240CE</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:24:17</t>
+        </is>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1883,8 +1887,12 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
+      <c r="AJ11" t="n">
+        <v>41.85</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1860,11 +1860,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-09-02 13:24:17</t>
-        </is>
-      </c>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1860,7 +1860,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:28:56</t>
+        </is>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1887,7 +1891,7 @@
         <v>41.85</v>
       </c>
       <c r="AK11" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1860,11 +1860,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-09-02 13:28:56</t>
-        </is>
-      </c>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1860,7 +1860,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:05:31</t>
+        </is>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1887,7 +1891,7 @@
         <v>41.85</v>
       </c>
       <c r="AK11" t="n">
-        <v>39.5</v>
+        <v>35.4</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1860,11 +1860,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-09-02 14:05:31</t>
-        </is>
-      </c>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1860,7 +1860,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:14:59</t>
+        </is>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1887,7 +1891,7 @@
         <v>41.85</v>
       </c>
       <c r="AK11" t="n">
-        <v>35.4</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1357,6 +1357,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:19:57</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1357,11 +1357,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-02 14:19:57</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1479,9 +1475,14 @@
           <t>NSE:NYKAA26SEP330CE</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:21:24</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 1 Hit</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1357,7 +1357,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:31:09</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1744,6 +1748,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:31:08</t>
+        </is>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1767,10 +1776,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>27.1</v>
+        <v>27.4</v>
       </c>
       <c r="AK10" t="n">
-        <v>25.55</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="11">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1357,11 +1357,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-02 14:31:09</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1746,11 +1742,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>Expired (no SL/Target hit)</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-09-02 14:31:08</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1357,7 +1357,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1612,9 +1611,14 @@
           <t>2026-09-02 11:44:08</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:33:31</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1903,6 +1903,125 @@
       <c r="AK11" t="n">
         <v>35</v>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:53:17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1650.6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1660</v>
+      </c>
+      <c r="I12" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="J12" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="K12" t="n">
+        <v>52.59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="M12" t="n">
+        <v>66.09</v>
+      </c>
+      <c r="N12" t="n">
+        <v>550</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="U12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:AUROPHARMA26SEP1660CE</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1992,12 +1992,6 @@
           <t>NSE:AUROPHARMA26SEP1660CE</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -2020,8 +2014,125 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:54:52</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>592.95</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H13" t="n">
+        <v>595</v>
+      </c>
+      <c r="I13" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="K13" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="M13" t="n">
+        <v>36.87</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1350</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="S13" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:KALYANKJIL26SEP595CE</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1992,6 +1992,16 @@
           <t>NSE:AUROPHARMA26SEP1660CE</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:56:26</t>
+        </is>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -2013,6 +2023,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>41.4</v>
       </c>
     </row>
     <row r="13">
@@ -2103,12 +2119,6 @@
           <t>NSE:KALYANKJIL26SEP595CE</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -2131,8 +2141,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -2119,6 +2119,16 @@
           <t>NSE:KALYANKJIL26SEP595CE</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:59:36</t>
+        </is>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -2140,6 +2150,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>23.6</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -2124,11 +2124,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-09-02 14:59:36</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1357,6 +1357,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:30</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1380,7 +1385,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1311.2</v>
+        <v>1500</v>
       </c>
       <c r="AK7" t="n">
         <v>1132.35</v>
@@ -2124,7 +2129,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:30</t>
+        </is>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -2148,10 +2157,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="AK13" t="n">
-        <v>23.6</v>
+        <v>21.6</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -2129,11 +2129,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-09-02 15:18:30</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1357,11 +1357,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-02 15:18:30</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -2129,7 +2125,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1357,7 +1357,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:24:44</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -2123,6 +2127,11 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:24:44</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -1357,11 +1357,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-02 15:24:44</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -2127,11 +2123,6 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>Expired (no SL/Target hit)</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-09-02 15:24:44</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -966,9 +966,14 @@
           <t>2026-09-02 12:50:23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:33:23</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1357,7 +1362,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -2129,6 +2129,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:34:02</t>
+        </is>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -2129,11 +2129,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-09-02 15:34:02</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/signals_2026-09-02.xlsx
@@ -834,9 +834,19 @@
           <t>NSE:HINDZINC26SEP580CE</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:46:00</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1098,9 +1108,19 @@
           <t>NSE:SONACOMS26SEP780CE</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:40:00</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:34:00</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1357,9 +1377,24 @@
           <t>NSE:BOSCHLTD26SEP47000CE</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-07 11:20:00</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-09-07 11:34:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:47:00</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1748,9 +1783,19 @@
           <t>NSE:SONACOMS26SEP780CE</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:40:00</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:34:00</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1870,9 +1915,14 @@
           <t>NSE:UNOMINDA26SEP1240CE</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:28:00</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1997,9 +2047,14 @@
           <t>NSE:AUROPHARMA26SEP1660CE</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:48:00</t>
+        </is>
+      </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2124,12 +2179,16 @@
           <t>NSE:KALYANKJIL26SEP595CE</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:21:00</t>
+        </is>
+      </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr"/>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
